--- a/data/trans_bre/IQ2605_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ2605_R2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,38</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 15,89</t>
+          <t>-1,12; 16,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 9,34</t>
+          <t>-6,73; 10,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,95; -2,73</t>
+          <t>-21,56; -2,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 20,53</t>
+          <t>-16,25; 19,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 42,12</t>
+          <t>-2,8; 45,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 12,51</t>
+          <t>-8,16; 13,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,65; -3,69</t>
+          <t>-26,03; -3,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 34,06</t>
+          <t>-20,71; 33,2</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-10,67</t>
+          <t>-10,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-12,09%</t>
+          <t>-11,86%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 2,03</t>
+          <t>-13,14; 1,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 8,16</t>
+          <t>-4,69; 8,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 6,55</t>
+          <t>-6,3; 6,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,64; 2,53</t>
+          <t>-25,38; 2,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,34; 3,82</t>
+          <t>-21,75; 3,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 11,16</t>
+          <t>-5,76; 11,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 8,83</t>
+          <t>-7,84; 8,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 3,02</t>
+          <t>-28,31; 3,05</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-5,15</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-1,73%</t>
+          <t>-7,49%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 14,48</t>
+          <t>-3,55; 15,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 4,93</t>
+          <t>-11,66; 4,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 5,78</t>
+          <t>-7,31; 5,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 18,92</t>
+          <t>-23,53; 16,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 35,88</t>
+          <t>-7,7; 36,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 6,76</t>
+          <t>-15,27; 6,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 7,04</t>
+          <t>-8,22; 6,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 31,83</t>
+          <t>-32,67; 27,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-4,22%</t>
+          <t>-3,13%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 7,88</t>
+          <t>-7,44; 8,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 9,66</t>
+          <t>-5,89; 9,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 4,97</t>
+          <t>-9,94; 4,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 13,24</t>
+          <t>-18,75; 14,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 13,86</t>
+          <t>-11,59; 15,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 15,46</t>
+          <t>-8,7; 16,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 6,85</t>
+          <t>-12,59; 6,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 20,3</t>
+          <t>-23,89; 22,94</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>-5,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-5,83%</t>
+          <t>-6,69%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,37</t>
+          <t>-3,1; 5,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 4,45</t>
+          <t>-3,5; 3,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,25</t>
+          <t>-6,86; 0,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 3,92</t>
+          <t>-13,23; 3,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 10,57</t>
+          <t>-5,64; 10,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 6,28</t>
+          <t>-4,65; 5,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 0,31</t>
+          <t>-8,46; 0,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 5,25</t>
+          <t>-16,57; 4,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2605_R2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IQ2605_R2-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-11,91</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,26</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-15,24%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>7.121182141788418</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.398429096696119</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-11.91201438231784</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.257527166833705</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1712836665794314</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.01803187684258653</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1524498370244574</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.01746006616448906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,12; 16,68</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,73; 10,19</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-21,56; -2,66</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-16,25; 19,64</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,8; 45,22</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-8,16; 13,95</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-26,03; -3,5</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-20,71; 33,2</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.121404000029108</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.733695863601316</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-21.5615883802339</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-16.24786115168295</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.02804981974217544</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.08158137175040354</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2602744334956699</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2071397607712308</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>16.67785512408438</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.18705858477144</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-2.660900650991365</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>19.64400884147267</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.452150857296056</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1395482719162779</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-0.03503939719336125</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.3319676574715864</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-5,75</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,6</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-10,43</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-9,99%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-0,26%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-11,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-13,14; 1,99</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,69; 8,43</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-6,3; 6,59</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-25,38; 2,67</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-21,75; 3,64</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-5,76; 11,21</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-7,84; 8,87</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-28,31; 3,05</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-5.752297511957027</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.596827004488255</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.2028779666795155</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-10.43089908089818</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.09994610994028857</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.02058321060543589</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.002605249867588192</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1186085606849729</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,52</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,4</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,94</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,15</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,08%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-4,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-1,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-7,49%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-13.14013944934119</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.690151127383238</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-6.295740777053446</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-25.38062443050717</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2175247612193833</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.05758340508286875</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.07836210933859462</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.283078434732651</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,55; 15,4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-11,66; 4,31</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,31; 5,7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-23,53; 16,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-7,7; 36,69</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-15,27; 6,37</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-8,22; 6,96</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-32,67; 27,07</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.992079873485152</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>8.429322256535405</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>6.586873235402041</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.669865242021557</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.03639643623524782</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1120552523018695</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.08874221085473862</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.03052079609707556</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-3,13%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.517051093119263</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.397852451716343</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9427731763883229</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-5.153105360824339</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.1208268013274494</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.04696448508172084</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.01098229957725041</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.07488900088464583</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-7,44; 8,68</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,89; 9,74</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-9,94; 4,64</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-18,75; 14,13</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-11,59; 15,3</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-8,7; 16,01</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-12,59; 6,42</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-23,89; 22,94</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.551250672938094</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.66402476997714</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-7.310597426666503</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-23.52612397693028</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.07701529162337903</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1527229062136942</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.08221200048745785</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3266764276967687</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>15.39586691668139</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.307007112469921</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.701558784950751</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>16.11218191865089</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.3669139410616817</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.06371353240550701</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.06960352516893699</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.270693568880935</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.04012027164990162</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.875713281757274</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.938126352011027</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.233902692775658</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.0006567108463234818</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.02839425735803896</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.02553351925070157</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.03132468444645915</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-7.43718947103902</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.890898842100133</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-9.941020224478518</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-18.74685682803868</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1159305426592865</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.08698363554358482</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1259263017037234</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.2389119916193539</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.684399728750563</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>9.740181390439933</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.637380423302353</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>14.12667560015424</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1530481328100673</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1601196771295551</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.06417255247321857</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.229359030377991</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,11</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,11</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-3,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-6,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,1; 5,48</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 3,96</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,86; 0,09</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-13,23; 3,42</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-5,64; 10,58</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-4,65; 5,57</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-8,46; 0,17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-16,57; 4,65</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.106065584966409</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3736818697691713</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-3.159160033088659</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-5.107941800459526</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.02093118306917435</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.005102766104736466</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.0399014313013596</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.06690871548552733</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.100487736028702</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.4984941046588</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-6.859868753305517</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-13.23146662025233</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.05644780080181084</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.04651677879560448</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.08455027958582431</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1656696221126695</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.483694473083508</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.96071043787095</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.0948525551437846</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.424689944129816</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1058007112315439</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.05574048590538836</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.001694597755322028</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.04646814411696432</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
